--- a/data/信用债发行汇总_2026-09-16.xlsx
+++ b/data/信用债发行汇总_2026-09-16.xlsx
@@ -1003,7 +1003,9 @@
           <t>2.65 ~ 2.80</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>珠海华发集团有限公司</t>
@@ -11460,7 +11462,11 @@
           <t>26太重MTN010(科创债)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>102683673.IB</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -11619,7 +11625,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -11980,7 +11988,11 @@
           <t>26涪陵实业MTN002B</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>102683683.IB</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -12506,7 +12518,11 @@
           <t>26寿光金旭MTN007</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>102683669.IB</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -12674,7 +12690,11 @@
           <t>26鲁黄金MTN001A</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>102683688.IB</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>20Y</t>
@@ -12837,7 +12857,9 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -12850,7 +12872,11 @@
           <t>26鲁黄金MTN001B</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>102683689.IB</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>30Y</t>
@@ -13013,7 +13039,9 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -13202,7 +13230,11 @@
           <t>26涪陵实业MTN002A</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>102683682.IB</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>7Y</t>
@@ -13378,7 +13410,11 @@
           <t>26诚泰租赁SCP003</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>012682272.IB</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -13722,7 +13758,11 @@
           <t>26新业国资MTN003</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>102683691.IB</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -13881,7 +13921,9 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AN17" s="2" t="inlineStr"/>
+      <c r="AN17" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -14070,7 +14112,11 @@
           <t>26津渤海MTN014</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>102683675.IB</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -14233,7 +14279,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -14418,7 +14466,11 @@
           <t>26济南轨交MTN003B</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>102683686.IB</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>10+N</t>
@@ -14590,7 +14642,11 @@
           <t>26中铁十一MTN004B</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>102683681.IB</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -14749,7 +14805,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -14934,7 +14992,11 @@
           <t>26潞安MTN007B</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>102683662.IB</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -16081,7 +16143,11 @@
           <t>26太重MTN010(科创债)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>102683673.IB</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -16240,7 +16306,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -16616,7 +16684,11 @@
           <t>26涪陵实业MTN002B</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>102683683.IB</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -17157,7 +17229,11 @@
           <t>26寿光金旭MTN007</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102683669.IB</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -17330,7 +17406,11 @@
           <t>26鲁黄金MTN001A</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>102683688.IB</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>20Y</t>
@@ -17493,7 +17573,9 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -17511,7 +17593,11 @@
           <t>26鲁黄金MTN001B</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>102683689.IB</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>30Y</t>
@@ -17674,7 +17760,9 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -17873,7 +17961,11 @@
           <t>26涪陵实业MTN002A</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>102683682.IB</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>7Y</t>
@@ -18054,7 +18146,11 @@
           <t>26诚泰租赁SCP003</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>012682272.IB</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -18408,7 +18504,11 @@
           <t>26新业国资MTN003</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>102683691.IB</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -18567,7 +18667,9 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -18766,7 +18868,11 @@
           <t>26津渤海MTN014</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>102683675.IB</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -18929,7 +19035,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -19124,7 +19232,11 @@
           <t>26济南轨交MTN003B</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>102683686.IB</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>10+N</t>
@@ -19301,7 +19413,11 @@
           <t>26中铁十一MTN004B</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>102683681.IB</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -19460,7 +19576,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -19655,7 +19773,11 @@
           <t>26潞安MTN007B</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>102683662.IB</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -20391,7 +20513,9 @@
           <t>2.60 ~ 3.60</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr"/>
+      <c r="H28" s="2" t="n">
+        <v>3.05</v>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
           <t>北京首都开发股份有限公司</t>
@@ -20578,7 +20702,9 @@
           <t>2.65 ~ 2.80</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="H29" s="2" t="n">
+        <v>2.8</v>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
           <t>珠海华发集团有限公司</t>
@@ -20952,7 +21078,9 @@
           <t>2.20 ~ 3.20</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="H31" s="2" t="n">
+        <v>2.24</v>
+      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
           <t>郑州航空港枢纽建设有限公司</t>
@@ -21316,7 +21444,9 @@
           <t>2.20 ~ 3.20</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
+      <c r="H33" s="2" t="n">
+        <v>2.36</v>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
           <t>青岛市城阳区阳光城阳控股集团有限公司</t>
@@ -21684,7 +21814,9 @@
           <t>2.10 ~ 2.70</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr"/>
+      <c r="H35" s="2" t="n">
+        <v>2.28</v>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
           <t>冀中能源集团有限责任公司</t>
@@ -22048,7 +22180,9 @@
           <t>1.80 ~ 2.50</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr"/>
+      <c r="H37" s="2" t="n">
+        <v>2.19</v>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
           <t>天津国有资本投资运营有限公司</t>
@@ -22208,12 +22342,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>26城控01</t>
+          <t>26城控01(取消发行)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>284055.SH</t>
+          <t>DY284055.SH</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -22294,7 +22428,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳区阳光城阳控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>青岛市城阳区阳光城阳控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
@@ -22349,11 +22483,7 @@
           <t>综合</t>
         </is>
       </c>
-      <c r="AJ38" s="2" t="inlineStr">
-        <is>
-          <t>2029-09-16</t>
-        </is>
-      </c>
+      <c r="AJ38" s="2" t="inlineStr"/>
       <c r="AK38" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -22410,7 +22540,9 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr"/>
+      <c r="H39" s="2" t="n">
+        <v>2.08</v>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>安阳发展投资集团有限公司</t>
@@ -22587,7 +22719,9 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr"/>
+      <c r="H40" s="2" t="n">
+        <v>2.17</v>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
           <t>恩施旅游集团有限公司</t>
@@ -22776,7 +22910,9 @@
           <t>2.00 ~ 2.50</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr"/>
+      <c r="H41" s="2" t="n">
+        <v>2.37</v>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t>三门峡市投资集团有限公司</t>
@@ -22959,7 +23095,9 @@
           <t>1.80 ~ 2.40</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr"/>
+      <c r="H42" s="2" t="n">
+        <v>2.02</v>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
           <t>冀中能源集团有限责任公司</t>
@@ -23331,7 +23469,9 @@
           <t>1.70 ~ 2.50</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr"/>
+      <c r="H44" s="2" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
           <t>淄博市城市资产运营集团有限公司</t>
